--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_1SEM.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_1SEM.xlsx
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ingT</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -630,55 +630,55 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.01398601398601399</v>
+        <v>0.04545454545454546</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>44</v>
+        <v>143</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.01398601398601399</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>tec</t>
+          <t>Tec</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>apmat</t>
+          <t>Apoio Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>appor</t>
+          <t>Apoio Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>mus</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>socem</t>
+          <t>Socioem.</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>ingT</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>apmat</t>
+          <t>Apoio Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>appor</t>
+          <t>Apoio Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mus</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1313,19 +1313,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>socem</t>
+          <t>Socioem.</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>tec</t>
+          <t>Tec</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>ing</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1540,7 +1540,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1612,7 +1612,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>tec</t>
+          <t>Tec</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1732,7 +1732,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1756,19 +1756,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Dei (Deise Hoffmann)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1780,19 +1780,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Dei (Deise Hoffmann)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1804,7 +1804,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>finan</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1900,7 +1900,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>plit</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1948,7 +1948,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>soc</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ing</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2199,19 +2199,19 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Dei (Deise Hoffmann)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -2223,19 +2223,19 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Dei (Deise Hoffmann)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>finan</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2415,19 +2415,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -2439,19 +2439,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>plit</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>tec</t>
+          <t>Tec</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2594,7 +2594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2618,7 +2618,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -2642,7 +2642,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ing</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2762,7 +2762,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2786,19 +2786,19 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>ADo (Andrea Domingos Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ADo (Andrea Domingos Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -2834,19 +2834,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2906,12 +2906,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -2930,12 +2930,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>plit</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -2954,7 +2954,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>soc</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -3109,7 +3109,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3205,7 +3205,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -3229,7 +3229,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3253,7 +3253,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>plit</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3325,7 +3325,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>soc</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3349,19 +3349,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>ADo (Andrea Domingos Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -3373,19 +3373,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ADo (Andrea Domingos Pereira)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ing</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -3600,7 +3600,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -3648,7 +3648,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3672,55 +3672,55 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06976744186046512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.06976744186046512</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3792,7 +3792,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -3816,7 +3816,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3840,7 +3840,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -3864,7 +3864,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ing</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>plit</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3912,19 +3912,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>Dei (Deise Hoffmann)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3936,19 +3936,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Dei (Deise Hoffmann)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3960,7 +3960,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3984,7 +3984,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>soc</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>plit</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>pred</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>qui</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>esp</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>ing</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4331,19 +4331,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt)</t>
+          <t>Dei (Deise Hoffmann)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -4355,19 +4355,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Dei (Deise Hoffmann)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -4379,19 +4379,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4403,19 +4403,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4427,12 +4427,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -4451,7 +4451,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>mat</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>soc</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_1SEM.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_1SEM.xlsx
@@ -570,13 +570,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05714285714285714</v>
+        <v>0.05825242718446602</v>
       </c>
     </row>
     <row r="4">
@@ -594,13 +594,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.06976744186046512</v>
       </c>
     </row>
     <row r="5">
@@ -618,13 +618,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.0379746835443038</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.04651162790697674</v>
       </c>
     </row>
     <row r="7">
@@ -666,13 +666,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.01398601398601399</v>
+        <v>0.01428571428571429</v>
       </c>
     </row>
     <row r="8">
@@ -690,13 +690,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -738,13 +738,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.01612903225806452</v>
       </c>
     </row>
     <row r="11">
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -924,13 +924,13 @@
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="9" t="n">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>21</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.0282258064516129</v>
+        <v>0.02884615384615385</v>
       </c>
     </row>
   </sheetData>
@@ -1013,13 +1013,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="4">
@@ -1037,13 +1037,13 @@
         <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.0379746835443038</v>
       </c>
     </row>
     <row r="5">
@@ -1061,13 +1061,13 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.01398601398601399</v>
+        <v>0.01428571428571429</v>
       </c>
     </row>
     <row r="6">
@@ -1085,13 +1085,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -1109,13 +1109,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02409638554216868</v>
+        <v>0.02469135802469136</v>
       </c>
     </row>
     <row r="8">
@@ -1157,13 +1157,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.01612903225806452</v>
       </c>
     </row>
     <row r="10">
@@ -1229,7 +1229,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1415,13 +1415,13 @@
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>15</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.02016129032258064</v>
+        <v>0.0206043956043956</v>
       </c>
     </row>
   </sheetData>
@@ -1504,13 +1504,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="4">
@@ -1528,13 +1528,13 @@
         <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06172839506172839</v>
+        <v>0.06329113924050633</v>
       </c>
     </row>
     <row r="5">
@@ -1576,13 +1576,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -1600,13 +1600,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
@@ -1624,13 +1624,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.09523809523809523</v>
       </c>
     </row>
     <row r="9">
@@ -1648,13 +1648,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.009708737864077669</v>
+        <v>0.009900990099009901</v>
       </c>
     </row>
     <row r="10">
@@ -1696,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.025</v>
+        <v>0.02564102564102564</v>
       </c>
     </row>
     <row r="12">
@@ -1720,13 +1720,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="13">
@@ -1744,13 +1744,13 @@
         <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
@@ -1768,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -1978,13 +1978,13 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>24</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03247631935047361</v>
+        <v>0.03310344827586207</v>
       </c>
     </row>
   </sheetData>
@@ -2067,13 +2067,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.09195402298850575</v>
+        <v>0.09411764705882353</v>
       </c>
     </row>
     <row r="4">
@@ -2091,13 +2091,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.03389830508474576</v>
       </c>
     </row>
     <row r="5">
@@ -2139,13 +2139,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.09523809523809523</v>
       </c>
     </row>
     <row r="7">
@@ -2163,13 +2163,13 @@
         <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.009708737864077669</v>
+        <v>0.009900990099009901</v>
       </c>
     </row>
     <row r="8">
@@ -2211,7 +2211,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2517,13 +2517,13 @@
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>16</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.02165087956698241</v>
+        <v>0.02206896551724138</v>
       </c>
     </row>
   </sheetData>
@@ -2606,13 +2606,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.1162790697674419</v>
       </c>
     </row>
     <row r="4">
@@ -2630,13 +2630,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03883495145631068</v>
+        <v>0.0392156862745098</v>
       </c>
     </row>
     <row r="5">
@@ -2654,13 +2654,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">
@@ -2678,13 +2678,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.03225806451612903</v>
       </c>
     </row>
     <row r="7">
@@ -2702,13 +2702,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03389830508474576</v>
       </c>
     </row>
     <row r="8">
@@ -2726,13 +2726,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04651162790697674</v>
+        <v>0.04878048780487805</v>
       </c>
     </row>
     <row r="9">
@@ -2750,13 +2750,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.01204819277108434</v>
+        <v>0.01234567901234568</v>
       </c>
     </row>
     <row r="10">
@@ -2846,7 +2846,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -2966,7 +2966,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3032,13 +3032,13 @@
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>19</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02490170380078637</v>
+        <v>0.02540106951871658</v>
       </c>
     </row>
   </sheetData>
@@ -3121,13 +3121,13 @@
         <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.08196721311475409</v>
       </c>
     </row>
     <row r="4">
@@ -3145,13 +3145,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.0396039603960396</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="5">
@@ -3169,13 +3169,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.09302325581395349</v>
+        <v>0.0975609756097561</v>
       </c>
     </row>
     <row r="6">
@@ -3193,13 +3193,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
@@ -3241,13 +3241,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04651162790697674</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
@@ -3265,13 +3265,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03174603174603174</v>
+        <v>0.03225806451612903</v>
       </c>
     </row>
     <row r="10">
@@ -3313,13 +3313,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01204819277108434</v>
+        <v>0.01234567901234568</v>
       </c>
     </row>
     <row r="12">
@@ -3385,7 +3385,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3523,13 +3523,13 @@
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>25</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.0327653997378768</v>
+        <v>0.03342245989304813</v>
       </c>
     </row>
   </sheetData>
@@ -3612,13 +3612,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1904761904761905</v>
       </c>
     </row>
     <row r="4">
@@ -3636,13 +3636,13 @@
         <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03488372093023256</v>
+        <v>0.03529411764705882</v>
       </c>
     </row>
     <row r="5">
@@ -3660,13 +3660,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.06976744186046512</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
@@ -3732,13 +3732,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.02352941176470588</v>
       </c>
     </row>
     <row r="9">
@@ -3756,13 +3756,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.015625</v>
       </c>
     </row>
     <row r="10">
@@ -3828,13 +3828,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.02325581395348837</v>
       </c>
     </row>
     <row r="13">
@@ -3852,13 +3852,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.01538461538461539</v>
+        <v>0.01587301587301587</v>
       </c>
     </row>
     <row r="14">
@@ -3876,13 +3876,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.01538461538461539</v>
+        <v>0.01587301587301587</v>
       </c>
     </row>
     <row r="15">
@@ -3948,7 +3948,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4014,13 +4014,13 @@
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>29</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.03527980535279805</v>
+        <v>0.03593556381660471</v>
       </c>
     </row>
   </sheetData>
@@ -4103,13 +4103,13 @@
         <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.09375</v>
+        <v>0.09836065573770492</v>
       </c>
     </row>
     <row r="4">
@@ -4127,13 +4127,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06557377049180328</v>
       </c>
     </row>
     <row r="5">
@@ -4175,13 +4175,13 @@
         <v>4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02469135802469136</v>
       </c>
     </row>
     <row r="7">
@@ -4199,13 +4199,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
@@ -4223,13 +4223,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.03278688524590164</v>
       </c>
     </row>
     <row r="9">
@@ -4319,13 +4319,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="13">
@@ -4367,7 +4367,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -4415,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4505,13 +4505,13 @@
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>24</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.03141361256544502</v>
+        <v>0.032</v>
       </c>
     </row>
   </sheetData>
